--- a/tables/tableLaserDiode.xlsx
+++ b/tables/tableLaserDiode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasia/Desktop/MATLAB_Godovova/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\greatuniter\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F18D03D-D3F2-0D41-9E44-B1F8AFD4362A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E1E9F4-09A8-44E3-8518-E35C2DE3C2EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2260" yWindow="460" windowWidth="10000" windowHeight="10800" tabRatio="861" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14865" yWindow="585" windowWidth="14400" windowHeight="10755" tabRatio="861" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,6 @@
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,48 +29,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>ФИО проверяющего</t>
+    <t>BoardNumber</t>
   </si>
   <si>
-    <t>Комментарий по проверке</t>
+    <t>DeviceType</t>
   </si>
   <si>
-    <t>текст комментария</t>
+    <t>Designation</t>
   </si>
   <si>
-    <t>Фамилия И.О.</t>
+    <t>SerialNumber</t>
   </si>
   <si>
-    <t>Смещение диапазона</t>
+    <t>Comment</t>
   </si>
   <si>
-    <t>Значение на ЦАП</t>
+    <t>InspectorName</t>
   </si>
   <si>
-    <t>Рабочая длина волны, нм</t>
+    <t>OperatingWavelength_nm</t>
   </si>
   <si>
-    <t>Номер платы</t>
+    <t>OffsetHighRange</t>
   </si>
   <si>
-    <t>Тип устройства</t>
+    <t>OutputOpticalPower_dBm</t>
   </si>
   <si>
-    <t>Обозначение на схеме</t>
-  </si>
-  <si>
-    <t>Серийный номер</t>
-  </si>
-  <si>
-    <t>Мощность на выходе, дБм</t>
-  </si>
-  <si>
-    <t>лазерный диод</t>
-  </si>
-  <si>
-    <t>Л1</t>
+    <t>DAC</t>
   </si>
 </sst>
 </file>
@@ -538,11 +525,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.5" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" customWidth="1"/>
-    <col min="4" max="11" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -552,52 +539,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BT61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.1640625" style="1" customWidth="1"/>
-    <col min="2" max="87" width="8.5" style="1" customWidth="1"/>
-    <col min="88" max="16384" width="9.33203125" style="1"/>
+    <col min="1" max="1" width="39.140625" style="1" customWidth="1"/>
+    <col min="2" max="87" width="8.42578125" style="1" customWidth="1"/>
+    <col min="88" max="16384" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
-      <c r="B1" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:72" ht="16" x14ac:dyDescent="0.2">
+      <c r="B1" s="7"/>
+    </row>
+    <row r="2" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:72" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:72" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="8">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="5" spans="1:72" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B2" s="10"/>
+    </row>
+    <row r="3" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
+      <c r="B3" s="10"/>
+    </row>
+    <row r="4" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8"/>
+    </row>
+    <row r="5" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -667,13 +644,11 @@
       <c r="BQ5" s="3"/>
       <c r="BR5" s="3"/>
     </row>
-    <row r="6" spans="1:72" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>3</v>
-      </c>
+      <c r="B6" s="7"/>
       <c r="C6" s="4"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -743,7 +718,7 @@
       <c r="BQ6" s="3"/>
       <c r="BR6" s="3"/>
     </row>
-    <row r="7" spans="1:72" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -819,9 +794,9 @@
       <c r="BQ7" s="3"/>
       <c r="BR7" s="3"/>
     </row>
-    <row r="8" spans="1:72" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2">
         <v>0</v>
@@ -895,9 +870,9 @@
       <c r="BQ8" s="3"/>
       <c r="BR8" s="3"/>
     </row>
-    <row r="9" spans="1:72" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2">
         <v>0</v>
@@ -971,9 +946,9 @@
       <c r="BQ9" s="3"/>
       <c r="BR9" s="3"/>
     </row>
-    <row r="10" spans="1:72" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2">
         <v>1023</v>
@@ -1049,7 +1024,7 @@
       <c r="BS10" s="2"/>
       <c r="BT10" s="2"/>
     </row>
-    <row r="11" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:72" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -1122,7 +1097,7 @@
       <c r="BS11" s="2"/>
       <c r="BT11" s="2"/>
     </row>
-    <row r="12" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:72" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -1195,7 +1170,7 @@
       <c r="BS12" s="2"/>
       <c r="BT12" s="2"/>
     </row>
-    <row r="13" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:72" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -1268,7 +1243,7 @@
       <c r="BS13" s="2"/>
       <c r="BT13" s="2"/>
     </row>
-    <row r="14" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:72" x14ac:dyDescent="0.25">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -1341,7 +1316,7 @@
       <c r="BS14" s="2"/>
       <c r="BT14" s="2"/>
     </row>
-    <row r="15" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:72" x14ac:dyDescent="0.25">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -1414,7 +1389,7 @@
       <c r="BS15" s="2"/>
       <c r="BT15" s="2"/>
     </row>
-    <row r="16" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:72" x14ac:dyDescent="0.25">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -1487,7 +1462,7 @@
       <c r="BS16" s="2"/>
       <c r="BT16" s="2"/>
     </row>
-    <row r="17" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -1560,7 +1535,7 @@
       <c r="BS17" s="2"/>
       <c r="BT17" s="2"/>
     </row>
-    <row r="18" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -1633,7 +1608,7 @@
       <c r="BS18" s="2"/>
       <c r="BT18" s="2"/>
     </row>
-    <row r="19" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -1706,7 +1681,7 @@
       <c r="BS19" s="2"/>
       <c r="BT19" s="2"/>
     </row>
-    <row r="20" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -1779,7 +1754,7 @@
       <c r="BS20" s="2"/>
       <c r="BT20" s="2"/>
     </row>
-    <row r="21" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -1852,7 +1827,7 @@
       <c r="BS21" s="2"/>
       <c r="BT21" s="2"/>
     </row>
-    <row r="22" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -1925,7 +1900,7 @@
       <c r="BS22" s="2"/>
       <c r="BT22" s="2"/>
     </row>
-    <row r="23" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -1998,7 +1973,7 @@
       <c r="BS23" s="2"/>
       <c r="BT23" s="2"/>
     </row>
-    <row r="24" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -2071,7 +2046,7 @@
       <c r="BS24" s="2"/>
       <c r="BT24" s="2"/>
     </row>
-    <row r="25" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -2144,7 +2119,7 @@
       <c r="BS25" s="2"/>
       <c r="BT25" s="2"/>
     </row>
-    <row r="26" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -2217,7 +2192,7 @@
       <c r="BS26" s="2"/>
       <c r="BT26" s="2"/>
     </row>
-    <row r="27" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -2288,7 +2263,7 @@
       <c r="BQ27" s="3"/>
       <c r="BR27" s="3"/>
     </row>
-    <row r="28" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -2359,7 +2334,7 @@
       <c r="BQ28" s="3"/>
       <c r="BR28" s="3"/>
     </row>
-    <row r="29" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -2430,7 +2405,7 @@
       <c r="BQ29" s="3"/>
       <c r="BR29" s="3"/>
     </row>
-    <row r="30" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -2501,7 +2476,7 @@
       <c r="BQ30" s="3"/>
       <c r="BR30" s="3"/>
     </row>
-    <row r="31" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -2572,7 +2547,7 @@
       <c r="BQ31" s="3"/>
       <c r="BR31" s="3"/>
     </row>
-    <row r="32" spans="2:72" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -2643,7 +2618,7 @@
       <c r="BQ32" s="3"/>
       <c r="BR32" s="3"/>
     </row>
-    <row r="33" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -2714,7 +2689,7 @@
       <c r="BQ33" s="3"/>
       <c r="BR33" s="3"/>
     </row>
-    <row r="34" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -2785,7 +2760,7 @@
       <c r="BQ34" s="3"/>
       <c r="BR34" s="3"/>
     </row>
-    <row r="35" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -2856,7 +2831,7 @@
       <c r="BQ35" s="3"/>
       <c r="BR35" s="3"/>
     </row>
-    <row r="36" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -2927,7 +2902,7 @@
       <c r="BQ36" s="3"/>
       <c r="BR36" s="3"/>
     </row>
-    <row r="37" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -2998,7 +2973,7 @@
       <c r="BQ37" s="3"/>
       <c r="BR37" s="3"/>
     </row>
-    <row r="38" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
@@ -3069,7 +3044,7 @@
       <c r="BQ38" s="3"/>
       <c r="BR38" s="3"/>
     </row>
-    <row r="39" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -3140,7 +3115,7 @@
       <c r="BQ39" s="3"/>
       <c r="BR39" s="3"/>
     </row>
-    <row r="40" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
@@ -3211,7 +3186,7 @@
       <c r="BQ40" s="3"/>
       <c r="BR40" s="3"/>
     </row>
-    <row r="41" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
@@ -3282,7 +3257,7 @@
       <c r="BQ41" s="3"/>
       <c r="BR41" s="3"/>
     </row>
-    <row r="42" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
@@ -3353,7 +3328,7 @@
       <c r="BQ42" s="3"/>
       <c r="BR42" s="3"/>
     </row>
-    <row r="43" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -3424,7 +3399,7 @@
       <c r="BQ43" s="3"/>
       <c r="BR43" s="3"/>
     </row>
-    <row r="44" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
@@ -3495,7 +3470,7 @@
       <c r="BQ44" s="3"/>
       <c r="BR44" s="3"/>
     </row>
-    <row r="45" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
@@ -3566,7 +3541,7 @@
       <c r="BQ45" s="3"/>
       <c r="BR45" s="3"/>
     </row>
-    <row r="46" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
@@ -3637,7 +3612,7 @@
       <c r="BQ46" s="3"/>
       <c r="BR46" s="3"/>
     </row>
-    <row r="47" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
@@ -3708,7 +3683,7 @@
       <c r="BQ47" s="3"/>
       <c r="BR47" s="3"/>
     </row>
-    <row r="48" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
@@ -3779,7 +3754,7 @@
       <c r="BQ48" s="3"/>
       <c r="BR48" s="3"/>
     </row>
-    <row r="49" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -3850,7 +3825,7 @@
       <c r="BQ49" s="3"/>
       <c r="BR49" s="3"/>
     </row>
-    <row r="50" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
@@ -3921,7 +3896,7 @@
       <c r="BQ50" s="3"/>
       <c r="BR50" s="3"/>
     </row>
-    <row r="51" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -3992,7 +3967,7 @@
       <c r="BQ51" s="3"/>
       <c r="BR51" s="3"/>
     </row>
-    <row r="52" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
@@ -4063,7 +4038,7 @@
       <c r="BQ52" s="3"/>
       <c r="BR52" s="3"/>
     </row>
-    <row r="53" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -4134,7 +4109,7 @@
       <c r="BQ53" s="3"/>
       <c r="BR53" s="3"/>
     </row>
-    <row r="54" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -4205,7 +4180,7 @@
       <c r="BQ54" s="3"/>
       <c r="BR54" s="3"/>
     </row>
-    <row r="55" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -4276,7 +4251,7 @@
       <c r="BQ55" s="3"/>
       <c r="BR55" s="3"/>
     </row>
-    <row r="56" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -4347,7 +4322,7 @@
       <c r="BQ56" s="3"/>
       <c r="BR56" s="3"/>
     </row>
-    <row r="57" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
@@ -4418,7 +4393,7 @@
       <c r="BQ57" s="3"/>
       <c r="BR57" s="3"/>
     </row>
-    <row r="58" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
@@ -4489,7 +4464,7 @@
       <c r="BQ58" s="3"/>
       <c r="BR58" s="3"/>
     </row>
-    <row r="59" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
@@ -4560,7 +4535,7 @@
       <c r="BQ59" s="3"/>
       <c r="BR59" s="3"/>
     </row>
-    <row r="60" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
@@ -4631,7 +4606,7 @@
       <c r="BQ60" s="3"/>
       <c r="BR60" s="3"/>
     </row>
-    <row r="61" spans="2:70" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:70" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>

--- a/tables/tableLaserDiode.xlsx
+++ b/tables/tableLaserDiode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\greatuniter\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E1E9F4-09A8-44E3-8518-E35C2DE3C2EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF33890-EAC4-4242-BD85-FED763C1E16D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14865" yWindow="585" windowWidth="14400" windowHeight="10755" tabRatio="861" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16425" yWindow="1755" windowWidth="14400" windowHeight="10755" tabRatio="861" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
